--- a/medford_lazery_khirurgicheskie.xlsx
+++ b/medford_lazery_khirurgicheskie.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1188,6 +1188,82 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Какой вид лазера самый эффективный?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>lazery_khirurgicheskie</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Какие существуют виды лазеров?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>lazery_khirurgicheskie</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>

--- a/medford_lazery_khirurgicheskie.xlsx
+++ b/medford_lazery_khirurgicheskie.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Лазеры хирургические для оснащения клиник и медицинских учреждений. В каталоге представлено 3 позиций.</t>
+          <t>Лазеры хирургические для оснащения клиник и медицинских учреждений.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_lazery_khirurgicheskie.xlsx
+++ b/medford_lazery_khirurgicheskie.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать лазеры хирургические для клиники?</t>
+          <t>Что такое хирургический лазер?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Страна производства, Производитель, Режим работы, Длина волны, нм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Хирургический лазер — аппарат, создающий концентрированный световой луч для точного разреза, испарения (вапоризации) и коагуляции мягких тканей. Луч одновременно запаивает мелкие сосуды, снижая кровопотерю, а высокая температура даёт стерилизующий эффект в зоне воздействия. Врач регулирует мощность и глубину под конкретную задачу.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Какие бывают виды хирургических лазеров?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Основные типы — CO₂ (углекислотные) для разрезов и поверхностной вапоризации, диодные для гемостаза и работы через гибкие световоды, а также неодимовые и эрбиевые для глубоких или точечных вмешательств. В нашей линейке представлены диодные системы KLS Martin Diomax и гинекологический лазер Deka SmartXide2 V2LR.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Чем диодный лазер отличается от CO₂?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены модели ведущих производителей. Подберём под ваши задачи и бюджет.</t>
+          <t>Диодный лазер компактнее, обеспечивает выраженный гемостаз и работает через гибкие световоды, что удобно в труднодоступных зонах и во флебологии. CO₂-лазер считается стандартом для поверхностных разрезов и вапоризации с минимальным нагревом вглубь. Выбор между ними зависит от типа ткани и характера операции.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Что означает класс лазера 4?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Класс 4 — высший по опасности: излучение способно повредить глаза и кожу, а также воспламенять материалы, поэтому обязательны защитные очки под длину волны, маркировка зоны и обученный персонал. Пилотный лазер (у Diomax 1550 — 635 нм, класс 3R) служит только для наведения и безопасен при штатном применении.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>В каких областях применяют хирургический лазер?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>По данным профильных источников, хирургические лазеры используют в общей хирургии, флебологии, гинекологии, отоларингологии, офтальмологии, нейрохирургии и стоматологии. Конкретный перечень вмешательств и показания к лазерному лечению определяет врач исходя из клинической ситуации и типа аппарата.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Какой вид лазера самый эффективный?</t>
+          <t>Какой лазер самый эффективный?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Единственного «самого эффективного» лазера не существует: результат зависит от совпадения длины волны с поглощением целевой ткани и от задачи. Для гемостаза эффективнее одни системы, для поверхностной абляции — другие. Поэтому аппарат подбирают под профиль вмешательств, а сравнение по одной лишь мощности некорректно.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Какие существуют виды лазеров?</t>
+          <t>Нужна ли лицензия и регистрация?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Хирургический лазер для клинического применения должен быть зарегистрированным медицинским изделием с действующим регистрационным удостоверением Росздравнадзора. Кроме того, работа с лазерами класса 4 требует соблюдения правил лазерной безопасности и обучения персонала. Статус регистрации уточняют до покупки.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Лазеры хирургические для оснащения клиник и медицинских учреждений.</t>
+          <t>Лазеры хирургические — аппараты, создающие концентрированный световой луч для разреза, вапоризации и коагуляции мягких тканей. В категории представлены диодные системы KLS Martin Diomax (Германия) и лазер для гинекологии Deka SmartXide2 V2LR (Италия). Модель Diomax 1550 работает на длине волны 1550 нм, относится к классу лазера 4, поддерживает непрерывный и импульсный режимы и хранит до 50 пользовательских программ. Хирургический лазер запаивает мелкие сосуды прямо в зоне разреза, снижая кровопотерю.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Типы хирургических лазеров</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое лазеры хирургические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3133,143 +3133,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Типы хирургических лазеров</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Тип лазера</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Особенность</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Страна производства</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Производитель</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Режим работы</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Длина волны, нм</t>
+          <t>Типичное применение</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Лазер для гинекологии Deka SmartXide2 V2LR</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>CO₂ (углекислотный)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>разрез и поверхностная вапоризация, минимальный нагрев вглубь</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Италия</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>67408</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>общая хирургия, гинекология, ЛОР</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Аппарат лазерный хирургический диодный KLS Martin Diomax</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>Диодный</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>компактный, гемостаз, работа через гибкие световоды</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Германия</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>67398</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>флебология, ЛОР, общая хирургия</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Аппарат лазерный хирургический диодный KLS Martin Diomax 1550</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>Неодимовый (Nd)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>глубокое воздействие</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>непрерывный, импульсный</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1550</t>
+          <t>специфические глубокие вмешательства</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Эрбиевый (Er)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>точечная абляция</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>точечные вмешательства</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3281,7 +3247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3607,12 +3573,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите специализацию</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается лазеры хирургические: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Сначала фиксируют область применения: флебология, гинекология, ЛОР, общая хирургия. От этого зависят требуемая длина волны и тип лазера. Специализированные системы, например Deka SmartXide2 V2LR для гинекологии, оптимизированы под свои задачи, тогда как диодные платформы универсальнее и работают в нескольких направлениях.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3652,12 +3618,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите тип лазера</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Тип подбирают под ткань и характер вмешательства: CO₂ — для разрезов и поверхностной вапоризации, диодный — для гемостаза и работы через световоды, неодимовый и эрбиевый — для глубоких или точечных воздействий. Универсального лазера нет; эффективность определяется совпадением длины волны с поглощением целевой ткани.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3697,12 +3663,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Сверьте длину волны и мощность</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Страна производства, Производитель, Режим работы, Длина волны, нм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Длина волны задаёт глубину и характер воздействия: у диодного KLS Martin Diomax 1550 это 1550 нм. Мощность и режим (непрерывный или импульсный) настраивают под протокол. Требуемые параметры сверяют с планируемыми процедурами; данные берут из паспорта аппарата, а не из общих утверждений.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -3742,12 +3708,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Учтите режимы и программы</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость.</t>
+          <t>Наличие импульсного и непрерывного режимов расширяет диапазон задач, а память программ ускоряет рутинную работу: Diomax 1550 хранит до 50 пользовательских настроек. Возможность сохранять протоколы под врача и тип вмешательства снижает риск ошибки настройки и стандартизирует результат в потоке.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -3787,12 +3753,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Обеспечьте лазерную безопасность</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Хирургические лазеры класса 4 требуют мер защиты: очки под конкретную длину волны, маркировку и ограничение доступа в зону, дымоотсос при вапоризации. Пилотный лазер (у Diomax — 635 нм, класс 3R) помогает наводить луч. Комплект средств безопасности и обучение персонала планируют вместе с покупкой аппарата.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -3832,12 +3798,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте регистрацию и сервис</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Для клинического применения аппарат должен быть зарегистрированным медицинским изделием с действующим РУ Росздравнадзора. Заранее уточняют условия гарантии, доступность оригинальных расходников и световодов, а также сервис — от этого зависит бесперебойность работы операционной.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -3887,7 +3853,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Лазеры хирургические подбирают под задачи отделения и совместимость с имеющимся оборудованием. При выборе обращают внимание на страна производства, производитель, режим работы, длина волны, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Хирургический лазер выбирают по длине волны и типу ткани, а не по универсальному «рейтингу мощности». Диодные системы с гибким световодом удобны там, где нужен гемостаз и доступ к труднодоступным зонам. Для клиники критично, чтобы аппарат класса 4 сопровождался средствами лазерной безопасности и обученным персоналом: защитными очками под конкретную длину волны, маркировкой зоны и корректно настроенными протоколами мощности.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4171,13 +4137,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое лазеры хирургические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Лазеры хирургические — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели ведущих производителей. Подберём вариант под задачи вашего отделения.</t>
+          <t>Хирургический лазер — медицинский аппарат, формирующий концентрированный луч для точного разреза, испарения и коагуляции тканей. Луч одновременно запаивает мелкие сосуды, создавая сухое операционное поле и снижая кровопотерю, а высокая температура даёт стерилизующий эффект. Основные типы — CO₂, диодные, неодимовые и эрбиевые лазеры; выбор зависит от типа ткани и задачи. Диодные системы, например KLS Martin Diomax 1550 (длина волны 1550 нм, класс 4, непрерывный и импульсный режимы), компактны и работают через гибкие световоды.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4214,13 +4180,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Хирургический лазер: принцип работы</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Страна производства, Производитель, Режим работы, Длина волны, нм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Хирургический лазер преобразует энергию в концентрированный световой луч, который нагревает ткань и позволяет её рассекать, испарять или коагулировать. Ключевое преимущество — бескровность: луч запаивает мелкие сосуды в зоне разреза, формируя сухое операционное поле. Высокая температура одновременно обеззараживает зону воздействия, а точная настройка защищает окружающие здоровые ткани.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4257,13 +4223,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Типы лазеров и их задачи</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>В хирургии применяют CO₂, диодные, неодимовые и эрбиевые лазеры. CO₂ подходят для разрезов и поверхностной вапоризации, диодные — для гемостаза и работы через световоды, неодимовые и эрбиевые — для глубоких и точечных вмешательств. Тип выбирают по длине волны и поглощению целевой ткани, поэтому под разные направления берут разные системы.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4300,13 +4266,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Параметры при выборе аппарата</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>При подборе хирургического лазера сравнивают длину волны (у KLS Martin Diomax 1550 — 1550 нм), класс лазера, режимы работы (непрерывный, импульсный) и наличие памяти программ (до 50 у Diomax 1550). Отдельно оценивают комплект лазерной безопасности, тип и совместимость световодов, а также сервисную поддержку и доступность расходников.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4323,6 +4289,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Безопасность и допуск в клинику</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Хирургические лазеры класса 4 требуют организованной лазерной безопасности: защитных очков под конкретную длину волны, маркировки и ограничения зоны, дымоотсоса при вапоризации, обученного персонала. Для законной эксплуатации в лечебном учреждении аппарат должен быть зарегистрированным медицинским изделием. Эти условия планируют одновременно с выбором самой системы.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>lazery_khirurgicheskie</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
